--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1323-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1323-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB4BE2A3-DA81-4F02-B90A-38BB6602133F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA8BF306-39D7-401F-B132-DF5FAB07F6F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{EB0BF5DB-0277-47D0-8D74-E8B4FF29CED4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EEDD30C5-E7A2-4266-AD55-A835A9EAE7D0}"/>
   </bookViews>
   <sheets>
     <sheet name="1323-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1598,29 +1598,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446B8FA3-911B-46C2-B56D-32FFB7A09EED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8078908C-5F8B-467B-87A7-6068B1D4844A}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1654,7 +1653,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1742,7 +1741,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1810,7 +1809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1882,7 +1881,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1954,7 +1953,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2098,7 +2097,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2170,7 +2169,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>6.26</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>5.54</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2458,7 +2457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2602,7 +2601,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="42">
         <v>2013</v>
       </c>
@@ -2674,7 +2673,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="44"/>
       <c r="B17" s="45"/>
       <c r="C17" s="18" t="s">
@@ -2702,7 +2701,7 @@
       <c r="W17" s="51"/>
       <c r="X17" s="47"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="52">
         <v>2012</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="54"/>
       <c r="B19" s="55"/>
       <c r="C19" s="20" t="s">
@@ -2802,7 +2801,7 @@
       <c r="W19" s="61"/>
       <c r="X19" s="57"/>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2011</v>
       </c>
@@ -2874,7 +2873,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2010</v>
       </c>
@@ -2946,7 +2945,7 @@
         <v>8.82</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="42">
         <v>2009</v>
       </c>
@@ -3018,7 +3017,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="44"/>
       <c r="B23" s="45"/>
       <c r="C23" s="18" t="s">
@@ -3046,7 +3045,7 @@
       <c r="W23" s="51"/>
       <c r="X23" s="47"/>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2008</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2007</v>
       </c>
@@ -3190,7 +3189,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="44"/>
       <c r="B26" s="45"/>
       <c r="C26" s="18" t="s">
@@ -3218,7 +3217,7 @@
       <c r="W26" s="51"/>
       <c r="X26" s="47"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2006</v>
       </c>
@@ -3290,7 +3289,7 @@
         <v>5.35</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2005</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="52">
         <v>2004</v>
       </c>
@@ -3434,7 +3433,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="54"/>
       <c r="B30" s="55"/>
       <c r="C30" s="20" t="s">
@@ -3462,7 +3461,7 @@
       <c r="W30" s="61"/>
       <c r="X30" s="57"/>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>2003</v>
       </c>
@@ -3534,7 +3533,7 @@
         <v>9.64</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
       <c r="C32" s="18" t="s">
@@ -3562,7 +3561,7 @@
       <c r="W32" s="51"/>
       <c r="X32" s="47"/>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="52">
         <v>2002</v>
       </c>
@@ -3634,7 +3633,7 @@
         <v>8.42</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="55"/>
       <c r="C34" s="20" t="s">
@@ -3662,7 +3661,7 @@
       <c r="W34" s="61"/>
       <c r="X34" s="57"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>2001</v>
       </c>
@@ -3734,7 +3733,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2000</v>
       </c>
@@ -3806,7 +3805,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="42">
         <v>1999</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="44"/>
       <c r="B38" s="45"/>
       <c r="C38" s="18" t="s">
@@ -3906,7 +3905,7 @@
       <c r="W38" s="51"/>
       <c r="X38" s="47"/>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="52">
         <v>1998</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="54"/>
       <c r="B40" s="55"/>
       <c r="C40" s="20" t="s">
@@ -4006,7 +4005,7 @@
       <c r="W40" s="61"/>
       <c r="X40" s="57"/>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>1997</v>
       </c>
@@ -4078,7 +4077,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1996</v>
       </c>
@@ -4150,7 +4149,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>1995</v>
       </c>
@@ -4222,7 +4221,7 @@
         <v>6.41</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="52">
         <v>1994</v>
       </c>
@@ -4294,7 +4293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="54"/>
       <c r="B45" s="55"/>
       <c r="C45" s="20" t="s">
@@ -4322,7 +4321,7 @@
       <c r="W45" s="61"/>
       <c r="X45" s="57"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1993</v>
       </c>
@@ -4394,7 +4393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1992</v>
       </c>
@@ -4466,7 +4465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40" t="s">
         <v>67</v>
       </c>
